--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488254_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488254_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6425</v>
+        <v>6.7207</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7018</v>
+        <v>6.9523</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0593</v>
+        <v>-0.2316</v>
       </c>
       <c r="G2" t="n">
         <v>4.5689</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2594</v>
+        <v>0.3376</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.092</v>
+        <v>0.1586</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3514</v>
+        <v>0.179</v>
       </c>
       <c r="V2" t="n">
         <v>1.2583</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3427</v>
+        <v>3.4964</v>
       </c>
       <c r="E3" t="n">
-        <v>4.717</v>
+        <v>4.6738</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3744</v>
+        <v>-1.1774</v>
       </c>
       <c r="G3" t="n">
         <v>3.0991</v>
@@ -688,13 +688,13 @@
         <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2393</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1131</v>
+        <v>-0.1564</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1261</v>
+        <v>0.0709</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6289</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1388</v>
+        <v>3.4643</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6897</v>
+        <v>3.7444</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.551</v>
+        <v>-0.2801</v>
       </c>
       <c r="G4" t="n">
         <v>2.0456</v>
@@ -766,13 +766,13 @@
         <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1477</v>
+        <v>0.1778</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1269</v>
+        <v>0.1816</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2746</v>
+        <v>-0.0037</v>
       </c>
       <c r="V4" t="n">
         <v>0.3144</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1094</v>
+        <v>2.2171</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6377</v>
+        <v>1.0409</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4716</v>
+        <v>1.1762</v>
       </c>
       <c r="G5" t="n">
         <v>0.9431</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4631</v>
+        <v>-0.3554</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0396</v>
+        <v>-0.6364</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5765</v>
+        <v>0.281</v>
       </c>
       <c r="V5" t="n">
         <v>1.2589</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4056</v>
+        <v>1.0617</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1778</v>
+        <v>-0.1437</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2278</v>
+        <v>1.2054</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3571</v>
+        <v>-2.0875</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2541</v>
+        <v>0.2304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1031</v>
+        <v>-2.3179</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0721</v>
+        <v>-1.0612</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0306</v>
+        <v>0.773</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0415</v>
+        <v>-1.8342</v>
       </c>
       <c r="M6" t="n">
-        <v>0.285</v>
+        <v>-1.0263</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2234</v>
+        <v>-0.5426</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0616</v>
+        <v>-0.4837</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6044</v>
+        <v>0.4641</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0321</v>
+        <v>-0.0258</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4278</v>
+        <v>0.4899</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0557</v>
+        <v>0.8446</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1005</v>
+        <v>-0.2613</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1561</v>
+        <v>1.1059</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0875</v>
+        <v>-1.2858</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2304</v>
+        <v>-1.6377</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3179</v>
+        <v>0.3519</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0612</v>
+        <v>1.1211</v>
       </c>
       <c r="K7" t="n">
-        <v>0.773</v>
+        <v>-0.4133</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8342</v>
+        <v>1.5344</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0263</v>
+        <v>-2.407</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5426</v>
+        <v>-1.2244</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4837</v>
+        <v>-1.1826</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1117</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4581</v>
+        <v>0.9283</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0174</v>
+        <v>-0.1573</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4407</v>
+        <v>1.0856</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5733</v>
+        <v>1.5727</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9433</v>
+        <v>0.6278</v>
       </c>
       <c r="X7" t="n">
-        <v>0.63</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6948</v>
+        <v>0.7453</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9035</v>
+        <v>0.3944</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5983</v>
+        <v>0.3509</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2858</v>
+        <v>1.3571</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6377</v>
+        <v>1.2541</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3519</v>
+        <v>0.1031</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1211</v>
+        <v>1.0721</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4133</v>
+        <v>1.0306</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5344</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.407</v>
+        <v>0.285</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2244</v>
+        <v>0.2234</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1826</v>
+        <v>0.0616</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3706</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7784</v>
+        <v>-0.056</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7996</v>
+        <v>0.2487</v>
       </c>
       <c r="U8" t="n">
-        <v>1.578</v>
+        <v>-0.3047</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5727</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6278</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1242</v>
+        <v>-0.1445</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7607</v>
+        <v>-0.5101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6365</v>
+        <v>0.3656</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5956</v>
@@ -1156,13 +1156,13 @@
         <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3243</v>
+        <v>0.304</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2524</v>
+        <v>-0.0019</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5767</v>
+        <v>0.3059</v>
       </c>
       <c r="V9" t="n">
         <v>1.2589</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5084</v>
+        <v>-0.2069</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2725</v>
+        <v>-1.3157</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7641</v>
+        <v>1.1088</v>
       </c>
       <c r="G10" t="n">
         <v>2.1253</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.2241</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2226</v>
+        <v>-0.2658</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1452</v>
+        <v>0.4899</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2594</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0128</v>
+        <v>-1.8349</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7547</v>
+        <v>-1.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2581</v>
+        <v>-0.135</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7078</v>
@@ -1312,13 +1312,13 @@
         <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4526</v>
+        <v>-0.2748</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3283</v>
+        <v>-0.2736</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1244</v>
+        <v>-0.0012</v>
       </c>
       <c r="V11" t="n">
         <v>0.63</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.181</v>
+        <v>-2.2537</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3794</v>
+        <v>-0.5752</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8016</v>
+        <v>-1.6785</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0488</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3855</v>
+        <v>0.3128</v>
       </c>
       <c r="T12" t="n">
-        <v>0.434</v>
+        <v>0.2381</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2589</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.5631</v>
+        <v>14.1101</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7527</v>
+        <v>12.2998</v>
       </c>
       <c r="F13" t="n">
-        <v>1.809999999999999</v>
+        <v>1.8102</v>
       </c>
       <c r="G13" t="n">
         <v>7.413600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>11.1171</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4301</v>
+        <v>1.977</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2372</v>
+        <v>-0.6902000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6671</v>
+        <v>2.6672</v>
       </c>
       <c r="V13" t="n">
         <v>4.7193</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4292</v>
+        <v>2.7723</v>
       </c>
       <c r="E14" t="n">
-        <v>1.441</v>
+        <v>1.7348</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9883</v>
+        <v>1.0375</v>
       </c>
       <c r="G14" t="n">
         <v>1.9697</v>
@@ -1546,13 +1546,13 @@
         <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1525</v>
+        <v>0.1906</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3283</v>
+        <v>-0.0345</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1758</v>
+        <v>0.2251</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3144</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>A. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4797</v>
+        <v>1.0044</v>
       </c>
       <c r="E16" t="n">
-        <v>2.228</v>
+        <v>2.3933</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7483</v>
+        <v>-1.3889</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0428</v>
+        <v>-1.0494</v>
       </c>
       <c r="H16" t="n">
-        <v>1.33</v>
+        <v>2.2133</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2872</v>
+        <v>-3.2627</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2902</v>
+        <v>2.4711</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1337</v>
+        <v>3.5683</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1565</v>
+        <v>-1.0971</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2474</v>
+        <v>-3.5205</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8037</v>
+        <v>-1.355</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4437</v>
+        <v>-2.1656</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1955</v>
+        <v>0.2077</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8643</v>
+        <v>-0.4452</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3313</v>
+        <v>0.6528</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3144</v>
+        <v>2.9578</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.1466</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>-0.1888</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LLAMAS JIMENEZ</t>
+          <t>D. MORILLO LEON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1939</v>
+        <v>0.7184</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3933</v>
+        <v>1.0151</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1994</v>
+        <v>-0.2967</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0494</v>
+        <v>0.2891</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2133</v>
+        <v>-1.5065</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.2627</v>
+        <v>1.7956</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4711</v>
+        <v>1.1158</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5683</v>
+        <v>-0.1805</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0971</v>
+        <v>1.2963</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.5205</v>
+        <v>-0.8267</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.355</v>
+        <v>-1.326</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1656</v>
+        <v>0.4993</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3972</v>
+        <v>0.0622</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4452</v>
+        <v>-0.1007</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8423</v>
+        <v>0.1629</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9578</v>
+        <v>-0.1888</v>
       </c>
       <c r="W17" t="n">
-        <v>3.1466</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.1888</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. BENÍTEZ SIERRA</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3221</v>
+        <v>0.6476</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3221</v>
+        <v>1.3467</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.699</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3221</v>
+        <v>0.0428</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3221</v>
+        <v>1.33</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.2872</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3221</v>
+        <v>2.2902</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3221</v>
+        <v>2.1337</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1565</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2.2474</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.8037</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.4437</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.3634</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.0171</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.3805</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MORILLO LEON</t>
+          <t>F. BENÍTEZ SIERRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.302</v>
+        <v>0.3221</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6234</v>
+        <v>0.3221</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3213</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2891</v>
+        <v>0.3221</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5065</v>
+        <v>0.3221</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7956</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1158</v>
+        <v>0.3221</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1805</v>
+        <v>0.3221</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2963</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8267</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.326</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4993</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3542</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4924</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1383</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1888</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.6308</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5187</v>
+        <v>0.4494</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1825</v>
+        <v>-1.0803</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2917</v>
+        <v>0.02</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7265</v>
+        <v>0.1091</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4348</v>
+        <v>-0.0891</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5654</v>
+        <v>0.4407</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3567</v>
+        <v>1.0521</v>
       </c>
       <c r="L20" t="n">
-        <v>2.2087</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.8571</v>
+        <v>-0.4207</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0833</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7738</v>
+        <v>0.5223</v>
       </c>
       <c r="P20" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2234</v>
+        <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0205</v>
+        <v>0.1107</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7511</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2693</v>
+        <v>0.102</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7632</v>
+        <v>-1.1321</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8182</v>
+        <v>-1.1321</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.833</v>
+        <v>-0.9813</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6397</v>
+        <v>-1.5418</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8067</v>
+        <v>0.5605</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5651</v>
@@ -2092,13 +2092,13 @@
         <v>0.7411</v>
       </c>
       <c r="S21" t="n">
-        <v>0.046</v>
+        <v>-0.1023</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5931</v>
+        <v>0.3469</v>
       </c>
       <c r="V21" t="n">
         <v>0.945</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0964</v>
+        <v>-1.5618</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0577</v>
+        <v>0.5394</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1541</v>
+        <v>-2.1012</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02</v>
+        <v>-0.2917</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1091</v>
+        <v>-0.7265</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0891</v>
+        <v>0.4348</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4407</v>
+        <v>3.5654</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0521</v>
+        <v>1.3567</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6114000000000001</v>
+        <v>2.2087</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4207</v>
+        <v>-3.8571</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-2.0833</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5223</v>
+        <v>-1.7738</v>
       </c>
       <c r="P22" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3706</v>
+        <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3549</v>
+        <v>0.1225</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.383</v>
+        <v>-0.2282</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0281</v>
+        <v>0.3506</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1321</v>
+        <v>-1.7632</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1321</v>
+        <v>-0.8182</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6011</v>
+        <v>-1.6368</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0561</v>
+        <v>-1.0119</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.545</v>
+        <v>-0.6249</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.152</v>
+        <v>-0.6417</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2257</v>
+        <v>-1.4403</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3778</v>
+        <v>0.7986</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5041</v>
+        <v>0.9303</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4211</v>
+        <v>-0.4596</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0829</v>
+        <v>1.3899</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6561</v>
+        <v>-1.572</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1954</v>
+        <v>-0.9807</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4607</v>
+        <v>-0.5913</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.24</v>
+        <v>-0.2366</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0037</v>
+        <v>-0.3858</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2437</v>
+        <v>0.1492</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1332</v>
+        <v>-0.9439</v>
       </c>
       <c r="W23" t="n">
         <v>-0.63</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5032</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3727</v>
+        <v>-1.9126</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5016</v>
+        <v>-0.2519</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8711</v>
+        <v>-1.6607</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6417</v>
+        <v>-0.152</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4403</v>
+        <v>0.2257</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7986</v>
+        <v>-0.3778</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9303</v>
+        <v>1.5041</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4596</v>
+        <v>1.4211</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3899</v>
+        <v>0.0829</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.572</v>
+        <v>-1.6561</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9807</v>
+        <v>-1.1954</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5913</v>
+        <v>-0.4607</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9724</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8754</v>
+        <v>-0.1996</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.097</v>
+        <v>0.1281</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9439</v>
+        <v>-1.1332</v>
       </c>
       <c r="W24" t="n">
         <v>-0.63</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3139</v>
+        <v>-0.5032</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2699</v>
+        <v>-6.648</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3133</v>
+        <v>-3.1175</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.9566</v>
+        <v>-3.5305</v>
       </c>
       <c r="G25" t="n">
         <v>-5.431</v>
@@ -2404,13 +2404,13 @@
         <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.192</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6056</v>
+        <v>-0.4097</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5865</v>
+        <v>-0.1604</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5733</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.6633</v>
+        <v>-7.2138</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.094</v>
+        <v>-5.8981</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5694</v>
+        <v>-1.3157</v>
       </c>
       <c r="G26" t="n">
         <v>-2.1367</v>
@@ -2482,13 +2482,13 @@
         <v>0.7411</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3032</v>
+        <v>-0.8537</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6019</v>
+        <v>-0.406</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7014</v>
+        <v>-0.4477</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2589</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.563</v>
+        <v>-12.91</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.810199999999999</v>
+        <v>-1.810099999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.7527</v>
+        <v>-11.0999</v>
       </c>
       <c r="G27" t="n">
         <v>-7.413600000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.843599999999999</v>
+        <v>-2.843600000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-4.5701</v>
@@ -2536,10 +2536,10 @@
         <v>12.2926</v>
       </c>
       <c r="K27" t="n">
-        <v>8.646299999999998</v>
+        <v>8.6463</v>
       </c>
       <c r="L27" t="n">
-        <v>3.6463</v>
+        <v>3.646300000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-19.7063</v>
@@ -2548,7 +2548,7 @@
         <v>-11.4899</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.216300000000002</v>
+        <v>-8.2163</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2560,19 +2560,19 @@
         <v>11.1171</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.43</v>
+        <v>-0.7771</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.6672</v>
+        <v>-2.6673</v>
       </c>
       <c r="U27" t="n">
-        <v>1.237</v>
+        <v>1.89</v>
       </c>
       <c r="V27" t="n">
         <v>-4.719399999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.3184000000000001</v>
+        <v>-0.3183999999999999</v>
       </c>
       <c r="X27" t="n">
         <v>-4.4011</v>
